--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AQ$56</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2223" uniqueCount="485">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -652,7 +652,225 @@
     <t>DocumentEntry.type</t>
   </si>
   <si>
-    <t>DocumentReference.type.id</t>
+    <t>DocumentReference.category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claxs
+</t>
+  </si>
+  <si>
+    <t>Categorization of document</t>
+  </si>
+  <si>
+    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
+  </si>
+  <si>
+    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>High-level kind of a clinical document at a macro level.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
+  </si>
+  <si>
+    <t>Composition.class</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
+  </si>
+  <si>
+    <t>DocumentEntry.class</t>
+  </si>
+  <si>
+    <t>DocumentReference.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who/what is the subject of the document</t>
+  </si>
+  <si>
+    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
+  </si>
+  <si>
+    <t>Event.subject</t>
+  </si>
+  <si>
+    <t>Composition.subject</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/recordTarget/</t>
+  </si>
+  <si>
+    <t>FiveWs.subject</t>
+  </si>
+  <si>
+    <t>PID-3 (No standard way to define a Practitioner or Group subject in HL7 v2 MDM message)</t>
+  </si>
+  <si>
+    <t>DocumentEntry.patientId</t>
+  </si>
+  <si>
+    <t>DocumentReference.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indexed
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">instant
+</t>
+  </si>
+  <si>
+    <t>Quand cette référence a été créée</t>
+  </si>
+  <si>
+    <t>When the document reference was created.</t>
+  </si>
+  <si>
+    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
+  </si>
+  <si>
+    <t>Event.occurrence[x]</t>
+  </si>
+  <si>
+    <t>Composition.date</t>
+  </si>
+  <si>
+    <t>.availabilityTime[type="TS"]</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>DocumentReference.author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who and/or what authored the document</t>
+  </si>
+  <si>
+    <t>Identifies who is responsible for adding the information to the document.</t>
+  </si>
+  <si>
+    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
+  </si>
+  <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>Composition.author</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUT"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/author</t>
+  </si>
+  <si>
+    <t>TXA-9 (No standard way to indicate a Device in HL7 v2 MDM message)</t>
+  </si>
+  <si>
+    <t>DocumentEntry.author</t>
+  </si>
+  <si>
+    <t>DocumentReference.authenticator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who/what authenticated the document</t>
+  </si>
+  <si>
+    <t>Which person or organization authenticates that this document is valid.</t>
+  </si>
+  <si>
+    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
+  </si>
+  <si>
+    <t>Composition.attester</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
+  </si>
+  <si>
+    <t>ClinicalDocument/legalAuthenticator</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>TXA-10</t>
+  </si>
+  <si>
+    <t>DocumentEntry.legalAuthenticator</t>
+  </si>
+  <si>
+    <t>DocumentReference.custodian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization which maintains the document</t>
+  </si>
+  <si>
+    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
+  </si>
+  <si>
+    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
+  </si>
+  <si>
+    <t>Composition.custodian</t>
+  </si>
+  <si>
+    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
+</t>
+  </si>
+  <si>
+    <t>Relationships to other documents</t>
+  </si>
+  <si>
+    <t>Relationships that this document has with other document references that already exist.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
+  </si>
+  <si>
+    <t>Composition.relatesTo</t>
+  </si>
+  <si>
+    <t>.outboundRelationship</t>
+  </si>
+  <si>
+    <t>DocumentEntry Associations</t>
+  </si>
+  <si>
+    <t>DocumentReference.relatesTo.id</t>
   </si>
   <si>
     <t xml:space="preserve">string
@@ -671,318 +889,13 @@
     <t>n/a</t>
   </si>
   <si>
-    <t>DocumentReference.type.extension</t>
+    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.extension:dataAbsentReason</t>
-  </si>
-  <si>
-    <t>dataAbsentReason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {data-absent-reason}
-</t>
-  </si>
-  <si>
-    <t>Type absent pour les documents référencés externes et internes</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value or elements in the element that is extended are missing.</t>
-  </si>
-  <si>
-    <t>ANY.nullFlavor</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>DocumentReference.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>DocumentReference.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">claxs
-</t>
-  </si>
-  <si>
-    <t>Categorization of document</t>
-  </si>
-  <si>
-    <t>A categorization for the type of document referenced - helps for indexing and searching. This may be implied by or derived from the code specified in the DocumentReference.type.</t>
-  </si>
-  <si>
-    <t>Key metadata element describing the the category or classification of the document. This is a broader perspective that groups similar documents based on how they would be used. This is a primary key used in searching.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level kind of a clinical document at a macro level.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
-  </si>
-  <si>
-    <t>Composition.class</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>Derived from a mapping of /ClinicalDocument/code/@code to an Affinity Domain specified coded value to use and coding system. Affinity Domains are encouraged to use the appropriate value for Type of Service, based on the LOINC Type of Service (see Page 53 of the LOINC User's Manual). Must be consistent with /ClinicalDocument/code/@code</t>
-  </si>
-  <si>
-    <t>DocumentEntry.class</t>
-  </si>
-  <si>
-    <t>DocumentReference.subject</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|Group|4.0.1|Device|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who/what is the subject of the document</t>
-  </si>
-  <si>
-    <t>Who or what the document is about. The document can be about a person, (patient or healthcare practitioner), a device (e.g. a machine) or even a group of subjects (such as a document about a herd of farm animals, or a set of patients that share a common exposure).</t>
-  </si>
-  <si>
-    <t>Event.subject</t>
-  </si>
-  <si>
-    <t>Composition.subject</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="SBJ"].role[typeCode="PAT"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/recordTarget/</t>
-  </si>
-  <si>
-    <t>FiveWs.subject</t>
-  </si>
-  <si>
-    <t>PID-3 (No standard way to define a Practitioner or Group subject in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.patientId</t>
-  </si>
-  <si>
-    <t>DocumentReference.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indexed
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
-</t>
-  </si>
-  <si>
-    <t>Quand cette référence a été créée</t>
-  </si>
-  <si>
-    <t>When the document reference was created.</t>
-  </si>
-  <si>
-    <t>Referencing/indexing time is used for tracking, organizing versions and searching.</t>
-  </si>
-  <si>
-    <t>Event.occurrence[x]</t>
-  </si>
-  <si>
-    <t>Composition.date</t>
-  </si>
-  <si>
-    <t>.availabilityTime[type="TS"]</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>DocumentReference.author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who and/or what authored the document</t>
-  </si>
-  <si>
-    <t>Identifies who is responsible for adding the information to the document.</t>
-  </si>
-  <si>
-    <t>Not necessarily who did the actual data entry (i.e. typist) or who was the source (informant).</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>Composition.author</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUT"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/author</t>
-  </si>
-  <si>
-    <t>TXA-9 (No standard way to indicate a Device in HL7 v2 MDM message)</t>
-  </si>
-  <si>
-    <t>DocumentEntry.author</t>
-  </si>
-  <si>
-    <t>DocumentReference.authenticator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Who/what authenticated the document</t>
-  </si>
-  <si>
-    <t>Which person or organization authenticates that this document is valid.</t>
-  </si>
-  <si>
-    <t>Represents a participant within the author institution who has legally authenticated or attested the document. Legal authentication implies that a document has been signed manually or electronically by the legal Authenticator.</t>
-  </si>
-  <si>
-    <t>Composition.attester</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="AUTHEN"].role[classCode="ASSIGNED"]</t>
-  </si>
-  <si>
-    <t>ClinicalDocument/legalAuthenticator</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>TXA-10</t>
-  </si>
-  <si>
-    <t>DocumentEntry.legalAuthenticator</t>
-  </si>
-  <si>
-    <t>DocumentReference.custodian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization which maintains the document</t>
-  </si>
-  <si>
-    <t>Identifies the organization or group who is responsible for ongoing maintenance of and access to the document.</t>
-  </si>
-  <si>
-    <t>Identifies the logical organization (software system, vendor, or department) to go to find the current version, where to report issues, etc. This is different from the physical location (URL, disk drive, or server) of the document, which is the technical location of the document, which host may be delegated to the management of some other organization.</t>
-  </si>
-  <si>
-    <t>Composition.custodian</t>
-  </si>
-  <si>
-    <t>.participation[typeCode="RCV"].role[classCode="CUST"].scoper[classCode="ORG" and determinerCode="INST"]</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>Relationships to other documents</t>
-  </si>
-  <si>
-    <t>Relationships that this document has with other document references that already exist.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because documents that append to other documents are incomplete on their own.</t>
-  </si>
-  <si>
-    <t>Composition.relatesTo</t>
-  </si>
-  <si>
-    <t>.outboundRelationship</t>
-  </si>
-  <si>
-    <t>DocumentEntry Associations</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.id</t>
-  </si>
-  <si>
-    <t>DocumentReference.relatesTo.extension</t>
   </si>
   <si>
     <t>DocumentReference.relatesTo.modifierExtension</t>
@@ -1172,6 +1085,16 @@
     <t>DocumentReference.content.attachment.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>DocumentReference.content.attachment.contentType</t>
   </si>
   <si>
@@ -1369,6 +1292,10 @@
   </si>
   <si>
     <t>DocumentReference.content.format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
   </si>
   <si>
     <t>Format/content rules for the document</t>
@@ -1909,12 +1836,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ61"/>
+  <dimension ref="A1:AQ56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="44.59765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="43.578125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.70703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -3319,7 +3246,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>163</v>
       </c>
@@ -3332,13 +3259,13 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>80</v>
@@ -3818,14 +3745,14 @@
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>80</v>
+        <v>206</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>80</v>
@@ -3834,10 +3761,10 @@
         <v>80</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>207</v>
@@ -3845,7 +3772,9 @@
       <c r="M16" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N16" s="2"/>
+      <c r="N16" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>80</v>
@@ -3870,13 +3799,13 @@
         <v>80</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>80</v>
+        <v>212</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>80</v>
@@ -3894,59 +3823,59 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>80</v>
+        <v>215</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>80</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ16" t="s" s="2">
-        <v>80</v>
+        <v>216</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>80</v>
@@ -3955,20 +3884,18 @@
         <v>80</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>139</v>
+        <v>218</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>80</v>
@@ -4005,66 +3932,64 @@
         <v>80</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>80</v>
+        <v>222</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>80</v>
+        <v>225</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>80</v>
+        <v>226</v>
       </c>
       <c r="AQ17" t="s" s="2">
-        <v>80</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C18" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4074,24 +3999,26 @@
         <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>80</v>
@@ -4140,34 +4067,34 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>80</v>
+        <v>234</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>80</v>
+        <v>235</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>222</v>
+        <v>236</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>80</v>
+        <v>237</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>80</v>
@@ -4178,10 +4105,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4204,20 +4131,18 @@
         <v>94</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>80</v>
       </c>
@@ -4265,7 +4190,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4280,33 +4205,33 @@
         <v>105</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>80</v>
+        <v>244</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>80</v>
+        <v>246</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="AQ19" t="s" s="2">
-        <v>80</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4326,23 +4251,21 @@
         <v>80</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>206</v>
+        <v>250</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O20" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>80</v>
       </c>
@@ -4390,7 +4313,7 @@
         <v>80</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4405,44 +4328,44 @@
         <v>105</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>80</v>
+        <v>254</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>80</v>
+        <v>256</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>80</v>
+        <v>257</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>239</v>
+        <v>258</v>
       </c>
       <c r="AQ20" t="s" s="2">
-        <v>80</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>241</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>80</v>
@@ -4451,19 +4374,19 @@
         <v>80</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>192</v>
+        <v>261</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4489,13 +4412,13 @@
         <v>80</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>246</v>
+        <v>80</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>247</v>
+        <v>80</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>80</v>
@@ -4513,13 +4436,13 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
@@ -4528,33 +4451,33 @@
         <v>105</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>80</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>249</v>
+        <v>266</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ21" t="s" s="2">
-        <v>251</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4565,7 +4488,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>80</v>
@@ -4577,15 +4500,17 @@
         <v>94</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>270</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -4634,13 +4559,13 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>80</v>
@@ -4649,37 +4574,37 @@
         <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>256</v>
+        <v>80</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>257</v>
+        <v>272</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>259</v>
+        <v>80</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>260</v>
+        <v>80</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>261</v>
+        <v>80</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>264</v>
+        <v>80</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4689,26 +4614,24 @@
         <v>93</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>268</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>80</v>
@@ -4757,7 +4680,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4769,22 +4692,22 @@
         <v>80</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>80</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>270</v>
+        <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>272</v>
+        <v>80</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>80</v>
@@ -4795,14 +4718,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4818,19 +4741,19 @@
         <v>80</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>275</v>
+        <v>140</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>277</v>
+        <v>142</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4880,7 +4803,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4892,28 +4815,28 @@
         <v>80</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>279</v>
+        <v>80</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>280</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>281</v>
+        <v>80</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>282</v>
+        <v>80</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>283</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -4925,26 +4848,26 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>285</v>
+        <v>139</v>
       </c>
       <c r="L25" t="s" s="2">
         <v>286</v>
@@ -4953,9 +4876,11 @@
         <v>287</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>142</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
       </c>
@@ -5003,48 +4928,48 @@
         <v>80</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>289</v>
+        <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>290</v>
+        <v>136</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>291</v>
+        <v>80</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>292</v>
+        <v>80</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>294</v>
+        <v>80</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5052,7 +4977,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
@@ -5064,19 +4989,19 @@
         <v>80</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>296</v>
+        <v>113</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -5102,13 +5027,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>80</v>
+        <v>294</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5126,10 +5051,10 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>93</v>
@@ -5141,13 +5066,13 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>278</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>80</v>
@@ -5159,15 +5084,15 @@
         <v>80</v>
       </c>
       <c r="AQ26" t="s" s="2">
-        <v>80</v>
+        <v>297</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5175,10 +5100,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>80</v>
@@ -5190,17 +5115,15 @@
         <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>80</v>
@@ -5249,13 +5172,13 @@
         <v>80</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>80</v>
@@ -5267,10 +5190,10 @@
         <v>80</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>80</v>
@@ -5282,15 +5205,15 @@
         <v>80</v>
       </c>
       <c r="AQ27" t="s" s="2">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5310,19 +5233,23 @@
         <v>80</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>206</v>
+        <v>276</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>207</v>
+        <v>306</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>80</v>
       </c>
@@ -5370,7 +5297,7 @@
         <v>80</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>209</v>
+        <v>305</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5382,7 +5309,7 @@
         <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>80</v>
@@ -5391,7 +5318,7 @@
         <v>80</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>210</v>
+        <v>310</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>80</v>
@@ -5400,22 +5327,22 @@
         <v>80</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>80</v>
+        <v>311</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>80</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5431,21 +5358,23 @@
         <v>80</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>140</v>
+        <v>314</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
       </c>
@@ -5469,13 +5398,13 @@
         <v>80</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>80</v>
+        <v>318</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>80</v>
+        <v>319</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>80</v>
@@ -5493,7 +5422,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>216</v>
+        <v>313</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5505,72 +5434,68 @@
         <v>80</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>80</v>
+        <v>321</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AQ29" t="s" s="2">
-        <v>80</v>
+        <v>325</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>139</v>
+        <v>268</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>328</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>80</v>
       </c>
@@ -5618,10 +5543,10 @@
         <v>80</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
@@ -5630,16 +5555,16 @@
         <v>80</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>80</v>
+        <v>329</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>136</v>
+        <v>330</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>80</v>
@@ -5656,10 +5581,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5667,7 +5592,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>93</v>
@@ -5679,20 +5604,18 @@
         <v>80</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -5717,13 +5640,13 @@
         <v>80</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>321</v>
+        <v>80</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>322</v>
+        <v>80</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>80</v>
@@ -5741,10 +5664,10 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>317</v>
+        <v>279</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>93</v>
@@ -5753,16 +5676,16 @@
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>323</v>
+        <v>80</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>324</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>80</v>
@@ -5774,26 +5697,26 @@
         <v>80</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>325</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>80</v>
@@ -5802,18 +5725,20 @@
         <v>80</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>327</v>
+        <v>139</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>328</v>
+        <v>140</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>80</v>
@@ -5862,28 +5787,28 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>330</v>
+        <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>280</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>80</v>
@@ -5895,7 +5820,7 @@
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>332</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5907,38 +5832,38 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J33" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>334</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>335</v>
+        <v>287</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>336</v>
+        <v>142</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>337</v>
+        <v>148</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -5987,19 +5912,19 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>333</v>
+        <v>288</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>80</v>
@@ -6008,7 +5933,7 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>338</v>
+        <v>136</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>80</v>
@@ -6017,18 +5942,18 @@
         <v>80</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>339</v>
+        <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>340</v>
+        <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6036,13 +5961,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>80</v>
@@ -6051,20 +5976,16 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>192</v>
+        <v>335</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>345</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
@@ -6088,13 +6009,13 @@
         <v>80</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>348</v>
+        <v>80</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>80</v>
@@ -6112,13 +6033,13 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>80</v>
@@ -6130,30 +6051,30 @@
         <v>80</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>353</v>
+        <v>341</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6161,28 +6082,28 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G35" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>355</v>
+        <v>277</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>356</v>
+        <v>278</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6233,28 +6154,28 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>354</v>
+        <v>279</v>
       </c>
       <c r="AG35" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH35" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AH35" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AI35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>357</v>
+        <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>358</v>
+        <v>280</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>80</v>
@@ -6271,21 +6192,21 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>80</v>
@@ -6297,15 +6218,17 @@
         <v>80</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6342,31 +6265,31 @@
         <v>80</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>80</v>
+        <v>344</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>80</v>
+        <v>345</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>80</v>
+        <v>144</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>80</v>
@@ -6375,7 +6298,7 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>210</v>
+        <v>280</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>80</v>
@@ -6392,21 +6315,21 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>80</v>
@@ -6415,21 +6338,21 @@
         <v>80</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>140</v>
+        <v>348</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O37" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
       </c>
@@ -6441,7 +6364,7 @@
         <v>80</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>80</v>
+        <v>351</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>80</v>
@@ -6453,13 +6376,13 @@
         <v>80</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>80</v>
+        <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>80</v>
+        <v>353</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>80</v>
@@ -6477,19 +6400,19 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>216</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>80</v>
@@ -6498,7 +6421,7 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>210</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>80</v>
@@ -6507,7 +6430,7 @@
         <v>80</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>80</v>
+        <v>356</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>80</v>
@@ -6515,45 +6438,43 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>314</v>
+        <v>358</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>148</v>
+        <v>360</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6566,7 +6487,7 @@
         <v>80</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>80</v>
+        <v>361</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>80</v>
@@ -6578,13 +6499,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6602,19 +6523,19 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>80</v>
@@ -6623,7 +6544,7 @@
         <v>80</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>136</v>
+        <v>363</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>80</v>
@@ -6638,12 +6559,12 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6651,31 +6572,35 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>80</v>
       </c>
@@ -6723,10 +6648,10 @@
         <v>80</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -6741,30 +6666,30 @@
         <v>80</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>367</v>
+        <v>80</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>369</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6784,19 +6709,23 @@
         <v>80</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>206</v>
+        <v>374</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>207</v>
+        <v>375</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
       </c>
@@ -6808,7 +6737,7 @@
         <v>80</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>80</v>
+        <v>379</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>80</v>
@@ -6844,7 +6773,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>209</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6856,7 +6785,7 @@
         <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>80</v>
@@ -6865,7 +6794,7 @@
         <v>80</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>210</v>
+        <v>381</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>80</v>
@@ -6874,7 +6803,7 @@
         <v>80</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>80</v>
+        <v>382</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>80</v>
@@ -6882,21 +6811,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>80</v>
@@ -6905,21 +6834,23 @@
         <v>80</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>384</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>140</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>212</v>
+        <v>386</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>387</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>388</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
       </c>
@@ -6955,31 +6886,31 @@
         <v>80</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>213</v>
+        <v>80</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>214</v>
+        <v>80</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>215</v>
+        <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>216</v>
+        <v>389</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>80</v>
@@ -6988,7 +6919,7 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>210</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>80</v>
@@ -7005,10 +6936,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7031,17 +6962,19 @@
         <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>113</v>
+        <v>365</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>393</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>394</v>
+      </c>
       <c r="O42" t="s" s="2">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7054,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>376</v>
+        <v>80</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>80</v>
@@ -7066,13 +6999,13 @@
         <v>80</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>377</v>
+        <v>80</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>80</v>
@@ -7090,7 +7023,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7111,7 +7044,7 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>80</v>
@@ -7120,7 +7053,7 @@
         <v>80</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>381</v>
+        <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>80</v>
@@ -7128,10 +7061,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7154,17 +7087,17 @@
         <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>276</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7177,7 +7110,7 @@
         <v>80</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>80</v>
@@ -7189,13 +7122,13 @@
         <v>80</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>80</v>
@@ -7213,7 +7146,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7234,7 +7167,7 @@
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>80</v>
@@ -7251,10 +7184,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7274,22 +7207,20 @@
         <v>80</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>409</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>80</v>
@@ -7338,7 +7269,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>395</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7359,7 +7290,7 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>80</v>
@@ -7368,7 +7299,7 @@
         <v>80</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>397</v>
+        <v>80</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>80</v>
@@ -7376,10 +7307,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7402,20 +7333,18 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>403</v>
-      </c>
+        <v>415</v>
+      </c>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>80</v>
       </c>
@@ -7427,7 +7356,7 @@
         <v>80</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>404</v>
+        <v>80</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>80</v>
@@ -7439,13 +7368,13 @@
         <v>80</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>80</v>
+        <v>416</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>80</v>
@@ -7463,7 +7392,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7481,30 +7410,30 @@
         <v>80</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>80</v>
+        <v>418</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>406</v>
+        <v>330</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>80</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>407</v>
+        <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>80</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7527,20 +7456,18 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>409</v>
+        <v>268</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>424</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>80</v>
       </c>
@@ -7588,7 +7515,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7609,7 +7536,7 @@
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>80</v>
@@ -7626,10 +7553,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7649,23 +7576,19 @@
         <v>80</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>390</v>
+        <v>276</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>417</v>
+        <v>277</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>80</v>
       </c>
@@ -7713,7 +7636,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>421</v>
+        <v>279</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7725,7 +7648,7 @@
         <v>80</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>80</v>
@@ -7734,7 +7657,7 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>422</v>
+        <v>280</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>80</v>
@@ -7751,21 +7674,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>80</v>
@@ -7774,21 +7697,21 @@
         <v>80</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>424</v>
+        <v>140</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>80</v>
       </c>
@@ -7800,7 +7723,7 @@
         <v>80</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>80</v>
@@ -7836,19 +7759,19 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>428</v>
+        <v>283</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>80</v>
@@ -7857,7 +7780,7 @@
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>429</v>
+        <v>280</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>80</v>
@@ -7874,43 +7797,45 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>80</v>
+        <v>285</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="J49" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>431</v>
+        <v>139</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>432</v>
+        <v>286</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="O49" t="s" s="2">
-        <v>434</v>
+        <v>148</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -7959,19 +7884,19 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>288</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>80</v>
@@ -7980,7 +7905,7 @@
         <v>80</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>415</v>
+        <v>136</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>80</v>
@@ -7997,10 +7922,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8011,7 +7936,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>80</v>
@@ -8020,20 +7945,18 @@
         <v>80</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>224</v>
+        <v>430</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>432</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -8058,13 +7981,13 @@
         <v>80</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>440</v>
+        <v>80</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>441</v>
+        <v>80</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -8082,13 +8005,13 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>80</v>
@@ -8097,33 +8020,33 @@
         <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>80</v>
+        <v>433</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>358</v>
+        <v>435</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>443</v>
+        <v>80</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>80</v>
+        <v>436</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>444</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8134,7 +8057,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>80</v>
@@ -8143,19 +8066,19 @@
         <v>80</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>303</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8181,13 +8104,13 @@
         <v>80</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>80</v>
+        <v>441</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>80</v>
+        <v>442</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -8205,13 +8128,13 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>80</v>
@@ -8223,10 +8146,10 @@
         <v>80</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>80</v>
+        <v>443</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>80</v>
@@ -8238,15 +8161,15 @@
         <v>80</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>80</v>
+        <v>445</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8266,16 +8189,16 @@
         <v>80</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>206</v>
+        <v>447</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>207</v>
+        <v>448</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>208</v>
+        <v>449</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8326,7 +8249,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>209</v>
+        <v>446</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8338,19 +8261,19 @@
         <v>80</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>80</v>
+        <v>450</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>210</v>
+        <v>451</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>80</v>
+        <v>452</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8359,26 +8282,26 @@
         <v>80</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>80</v>
+        <v>453</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>138</v>
+        <v>80</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>80</v>
@@ -8390,17 +8313,15 @@
         <v>80</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>140</v>
+        <v>455</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="N53" s="2"/>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>80</v>
@@ -8425,13 +8346,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>80</v>
+        <v>457</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>80</v>
+        <v>458</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8449,31 +8370,31 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>216</v>
+        <v>454</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>210</v>
+        <v>460</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>80</v>
+        <v>461</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8482,50 +8403,50 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>80</v>
+        <v>462</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>313</v>
+        <v>80</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>314</v>
+        <v>464</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>315</v>
+        <v>465</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>142</v>
+        <v>466</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>148</v>
+        <v>467</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8550,13 +8471,13 @@
         <v>80</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>80</v>
+        <v>210</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>80</v>
+        <v>468</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>80</v>
+        <v>469</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>80</v>
@@ -8574,31 +8495,31 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>316</v>
+        <v>463</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>136</v>
+        <v>460</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>80</v>
+        <v>459</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8607,15 +8528,15 @@
         <v>80</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>80</v>
+        <v>470</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8626,7 +8547,7 @@
         <v>81</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>80</v>
@@ -8638,13 +8559,13 @@
         <v>80</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8695,13 +8616,13 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>80</v>
@@ -8710,33 +8631,33 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>457</v>
+        <v>80</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>458</v>
+        <v>222</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>459</v>
+        <v>223</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>80</v>
+        <v>224</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>460</v>
+        <v>80</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>80</v>
+        <v>475</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8750,7 +8671,7 @@
         <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>80</v>
@@ -8759,16 +8680,16 @@
         <v>80</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>477</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>462</v>
+        <v>478</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>463</v>
+        <v>479</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>464</v>
+        <v>480</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8794,13 +8715,13 @@
         <v>80</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>465</v>
+        <v>80</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>466</v>
+        <v>80</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -8818,7 +8739,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>461</v>
+        <v>476</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8836,13 +8757,13 @@
         <v>80</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>80</v>
+        <v>483</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -8851,622 +8772,11 @@
         <v>80</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
-      <c r="P57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ57" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" s="2"/>
-      <c r="P58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM58" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ60" t="s" s="2">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ61" t="s" s="2">
-        <v>508</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ61">
+  <autoFilter ref="A1:AQ56">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9476,7 +8786,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI55">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-document-reference-document.xlsx
+++ b/main/ig/StructureDefinition-fr-document-reference-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
